--- a/03_Outputs/all/03_DS/ds_idx8_demografica.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx8_demografica.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>4.544793342146825</v>
+        <v>4.544793342146826</v>
       </c>
       <c r="D2">
-        <v>-0.3270119637137279</v>
+        <v>-0.3270119637137281</v>
       </c>
       <c r="E2">
-        <v>1.384023043110534</v>
+        <v>1.384023043110535</v>
       </c>
       <c r="F2">
-        <v>0.3492916269637692</v>
+        <v>0.3492916269637665</v>
       </c>
       <c r="G2">
-        <v>0.4636907851887331</v>
+        <v>0.4636907851887313</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-1.091064574655667</v>
+        <v>-1.091064574655668</v>
       </c>
       <c r="D3">
-        <v>1.383040728597262</v>
+        <v>1.38304072859726</v>
       </c>
       <c r="E3">
         <v>-0.3863653584259867</v>
       </c>
       <c r="F3">
-        <v>0.6222913760577384</v>
+        <v>0.6222913760577391</v>
       </c>
       <c r="G3">
-        <v>0.2841905567464361</v>
+        <v>0.2841905567464358</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.6094982506555263</v>
+        <v>-0.6094982506555265</v>
       </c>
       <c r="D4">
-        <v>1.640619992969873</v>
+        <v>1.640619992969871</v>
       </c>
       <c r="E4">
-        <v>-0.6165975580751556</v>
+        <v>-0.6165975580751566</v>
       </c>
       <c r="F4">
-        <v>0.4161102126920326</v>
+        <v>0.4161102126920335</v>
       </c>
       <c r="G4">
-        <v>-0.05972580349242229</v>
+        <v>-0.0597258034924238</v>
       </c>
     </row>
     <row r="5">
@@ -487,16 +487,16 @@
         <v>-2.269205878233932</v>
       </c>
       <c r="D5">
-        <v>1.006134475334676</v>
+        <v>1.006134475334675</v>
       </c>
       <c r="E5">
-        <v>0.5964156287133136</v>
+        <v>0.596415628713315</v>
       </c>
       <c r="F5">
-        <v>1.148492374923583</v>
+        <v>1.148492374923581</v>
       </c>
       <c r="G5">
-        <v>0.1248200946877509</v>
+        <v>0.1248200946877505</v>
       </c>
     </row>
     <row r="6">
@@ -514,16 +514,16 @@
         <v>3.237413952377498</v>
       </c>
       <c r="D6">
-        <v>-0.4688928836546841</v>
+        <v>-0.4688928836546868</v>
       </c>
       <c r="E6">
-        <v>-0.7764308999048976</v>
+        <v>-0.7764308999048979</v>
       </c>
       <c r="F6">
-        <v>-0.1606670366801361</v>
+        <v>-0.1606670366801335</v>
       </c>
       <c r="G6">
-        <v>-0.2581476881375352</v>
+        <v>-0.2581476881375364</v>
       </c>
     </row>
     <row r="7">
@@ -541,16 +541,16 @@
         <v>1.148944993681231</v>
       </c>
       <c r="D7">
-        <v>-0.2666698238686269</v>
+        <v>-0.2666698238686292</v>
       </c>
       <c r="E7">
-        <v>0.2634321513314312</v>
+        <v>0.2634321513314309</v>
       </c>
       <c r="F7">
-        <v>0.04668648375224978</v>
+        <v>0.0466864837522489</v>
       </c>
       <c r="G7">
-        <v>-0.2905721073082413</v>
+        <v>-0.2905721073082437</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>1.851608195461147</v>
       </c>
       <c r="D8">
-        <v>-0.4253363299325817</v>
+        <v>-0.4253363299325842</v>
       </c>
       <c r="E8">
-        <v>0.03051944361763585</v>
+        <v>0.0305194436176316</v>
       </c>
       <c r="F8">
-        <v>-1.61274107986773</v>
+        <v>-1.612741079867729</v>
       </c>
       <c r="G8">
-        <v>0.02951155776425843</v>
+        <v>0.02951155776425768</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.8269702675782556</v>
+        <v>0.8269702675782558</v>
       </c>
       <c r="D9">
-        <v>0.2714321456054838</v>
+        <v>0.2714321456054809</v>
       </c>
       <c r="E9">
-        <v>-0.247104191477987</v>
+        <v>-0.2471041914779893</v>
       </c>
       <c r="F9">
         <v>-0.4730888206396352</v>
       </c>
       <c r="G9">
-        <v>-0.7562581814804455</v>
+        <v>-0.7562581814804473</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.02482103499706806</v>
+        <v>-0.02482103499706767</v>
       </c>
       <c r="D10">
-        <v>0.4026160444920059</v>
+        <v>0.4026160444920025</v>
       </c>
       <c r="E10">
-        <v>-1.119365659408379</v>
+        <v>-1.11936565940838</v>
       </c>
       <c r="F10">
-        <v>-0.2452402404482452</v>
+        <v>-0.2452402404482424</v>
       </c>
       <c r="G10">
-        <v>-0.870270225462292</v>
+        <v>-0.8702702254622922</v>
       </c>
     </row>
     <row r="11">
@@ -649,16 +649,16 @@
         <v>0.1810567077968629</v>
       </c>
       <c r="D11">
-        <v>-0.09443488417238124</v>
+        <v>-0.09443488417238338</v>
       </c>
       <c r="E11">
-        <v>-0.9622112815132963</v>
+        <v>-0.962211281513294</v>
       </c>
       <c r="F11">
-        <v>1.068770044197134</v>
+        <v>1.068770044197137</v>
       </c>
       <c r="G11">
-        <v>0.1435145383219992</v>
+        <v>0.1435145383219996</v>
       </c>
     </row>
     <row r="12">
@@ -676,16 +676,16 @@
         <v>1.708469543668348</v>
       </c>
       <c r="D12">
-        <v>-1.229588029363485</v>
+        <v>-1.229588029363487</v>
       </c>
       <c r="E12">
-        <v>0.08253915176584281</v>
+        <v>0.08253915176584353</v>
       </c>
       <c r="F12">
-        <v>0.01216735223824894</v>
+        <v>0.01216735223824941</v>
       </c>
       <c r="G12">
-        <v>0.4320103718340465</v>
+        <v>0.4320103718340458</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.2175604364156788</v>
+        <v>-0.2175604364156784</v>
       </c>
       <c r="D13">
-        <v>1.055647758205002</v>
+        <v>1.055647758204999</v>
       </c>
       <c r="E13">
-        <v>-1.234279320780712</v>
+        <v>-1.234279320780713</v>
       </c>
       <c r="F13">
-        <v>0.05999410433965685</v>
+        <v>0.05999410433965939</v>
       </c>
       <c r="G13">
-        <v>-0.800594697645177</v>
+        <v>-0.8005946976451783</v>
       </c>
     </row>
     <row r="14">
@@ -730,16 +730,16 @@
         <v>3.190433605381159</v>
       </c>
       <c r="D14">
-        <v>-1.833941707881853</v>
+        <v>-1.833941707881855</v>
       </c>
       <c r="E14">
-        <v>0.03513933418313483</v>
+        <v>0.03513933418314022</v>
       </c>
       <c r="F14">
-        <v>1.691754574036043</v>
+        <v>1.691754574036044</v>
       </c>
       <c r="G14">
-        <v>0.2988372384005276</v>
+        <v>0.2988372384005265</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-3.018164930235934</v>
+        <v>-3.018164930235933</v>
       </c>
       <c r="D15">
-        <v>-1.388702877342442</v>
+        <v>-1.388702877342445</v>
       </c>
       <c r="E15">
-        <v>-1.065014383195509</v>
+        <v>-1.065014383195507</v>
       </c>
       <c r="F15">
-        <v>1.02360377418621</v>
+        <v>1.023603774186212</v>
       </c>
       <c r="G15">
-        <v>0.4037347093179064</v>
+        <v>0.4037347093179054</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-2.741414293165646</v>
+        <v>-2.741414293165647</v>
       </c>
       <c r="D16">
-        <v>1.131650122430636</v>
+        <v>1.131650122430634</v>
       </c>
       <c r="E16">
-        <v>0.2828657911501926</v>
+        <v>0.2828657911501942</v>
       </c>
       <c r="F16">
-        <v>1.244308363234941</v>
+        <v>1.244308363234939</v>
       </c>
       <c r="G16">
-        <v>0.1276320715896314</v>
+        <v>0.1276320715896291</v>
       </c>
     </row>
     <row r="17">
@@ -811,16 +811,16 @@
         <v>-3.401912540226986</v>
       </c>
       <c r="D17">
-        <v>0.6967642227367864</v>
+        <v>0.6967642227367843</v>
       </c>
       <c r="E17">
-        <v>0.3335953128900855</v>
+        <v>0.3335953128900818</v>
       </c>
       <c r="F17">
-        <v>-0.9764891606571794</v>
+        <v>-0.9764891606571803</v>
       </c>
       <c r="G17">
-        <v>0.1697444149090029</v>
+        <v>0.1697444149090037</v>
       </c>
     </row>
     <row r="18">
@@ -838,16 +838,16 @@
         <v>3.425800247518983</v>
       </c>
       <c r="D18">
-        <v>-0.2455274835256858</v>
+        <v>-0.2455274835256884</v>
       </c>
       <c r="E18">
-        <v>-0.8468381070619552</v>
+        <v>-0.8468381070619573</v>
       </c>
       <c r="F18">
-        <v>-0.7392435536155747</v>
+        <v>-0.7392435536155718</v>
       </c>
       <c r="G18">
-        <v>-0.1893770869638267</v>
+        <v>-0.1893770869638275</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>1.2749492090034</v>
+        <v>1.274949209003401</v>
       </c>
       <c r="D19">
-        <v>0.6233495195651128</v>
+        <v>0.6233495195651098</v>
       </c>
       <c r="E19">
-        <v>-1.208869917169368</v>
+        <v>-1.208869917169369</v>
       </c>
       <c r="F19">
-        <v>-0.1639900101053802</v>
+        <v>-0.1639900101053773</v>
       </c>
       <c r="G19">
-        <v>-0.4498519168196088</v>
+        <v>-0.4498519168196096</v>
       </c>
     </row>
     <row r="20">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>4.757057986531564</v>
+        <v>4.757057986531563</v>
       </c>
       <c r="D20">
         <v>-1.472170040585342</v>
@@ -898,10 +898,10 @@
         <v>1.492851261678299</v>
       </c>
       <c r="F20">
-        <v>-0.4708847447763279</v>
+        <v>-0.4708847447763306</v>
       </c>
       <c r="G20">
-        <v>0.4052238069936389</v>
+        <v>0.4052238069936373</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.5195574554083703</v>
+        <v>-0.5195574554083704</v>
       </c>
       <c r="D21">
-        <v>1.26688840753138</v>
+        <v>1.266888407531377</v>
       </c>
       <c r="E21">
-        <v>-0.3429151305399142</v>
+        <v>-0.342915130539915</v>
       </c>
       <c r="F21">
-        <v>0.3248821523103111</v>
+        <v>0.3248821523103114</v>
       </c>
       <c r="G21">
-        <v>-0.4709070604069156</v>
+        <v>-0.4709070604069165</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.6083090667077142</v>
+        <v>0.6083090667077145</v>
       </c>
       <c r="D22">
-        <v>-0.1670877529740438</v>
+        <v>-0.1670877529740472</v>
       </c>
       <c r="E22">
-        <v>-1.172872070904814</v>
+        <v>-1.172872070904816</v>
       </c>
       <c r="F22">
-        <v>-0.3463031889835774</v>
+        <v>-0.3463031889835746</v>
       </c>
       <c r="G22">
-        <v>-0.4285637697558247</v>
+        <v>-0.4285637697558255</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.2397881647293995</v>
+        <v>0.2397881647293992</v>
       </c>
       <c r="D23">
-        <v>0.5508508577277487</v>
+        <v>0.5508508577277472</v>
       </c>
       <c r="E23">
-        <v>0.9531952474801637</v>
+        <v>0.9531952474801622</v>
       </c>
       <c r="F23">
-        <v>-0.2031268679556632</v>
+        <v>-0.2031268679556656</v>
       </c>
       <c r="G23">
-        <v>-0.1930741713861272</v>
+        <v>-0.1930741713861291</v>
       </c>
     </row>
     <row r="24">
@@ -1000,16 +1000,16 @@
         <v>-0.8596980857678711</v>
       </c>
       <c r="D24">
-        <v>-1.09879326631407</v>
+        <v>-1.098793266314074</v>
       </c>
       <c r="E24">
-        <v>-1.438978257744074</v>
+        <v>-1.43897825774407</v>
       </c>
       <c r="F24">
-        <v>1.136167763124271</v>
+        <v>1.136167763124274</v>
       </c>
       <c r="G24">
-        <v>-0.08834089028703725</v>
+        <v>-0.08834089028703745</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.2767596587934692</v>
+        <v>-0.2767596587934691</v>
       </c>
       <c r="D25">
-        <v>0.4120138931510686</v>
+        <v>0.4120138931510667</v>
       </c>
       <c r="E25">
-        <v>-0.983749356918823</v>
+        <v>-0.9837493569188287</v>
       </c>
       <c r="F25">
-        <v>-1.973287421632396</v>
+        <v>-1.973287421632393</v>
       </c>
       <c r="G25">
-        <v>1.0811990260501</v>
+        <v>1.081199026050102</v>
       </c>
     </row>
     <row r="26">
@@ -1054,13 +1054,13 @@
         <v>-3.58197409936527</v>
       </c>
       <c r="D26">
-        <v>0.05084743905248875</v>
+        <v>0.05084743905248468</v>
       </c>
       <c r="E26">
-        <v>-0.6828639174641453</v>
+        <v>-0.682863917464146</v>
       </c>
       <c r="F26">
-        <v>0.2409410995509721</v>
+        <v>0.2409410995509728</v>
       </c>
       <c r="G26">
         <v>-1.295463714328486</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.5362172851585191</v>
+        <v>0.5362172851585196</v>
       </c>
       <c r="D27">
-        <v>-0.5292517324944204</v>
+        <v>-0.5292517324944245</v>
       </c>
       <c r="E27">
-        <v>-1.689348440951821</v>
+        <v>-1.689348440951822</v>
       </c>
       <c r="F27">
-        <v>-0.335729953068124</v>
+        <v>-0.3357299530681197</v>
       </c>
       <c r="G27">
-        <v>-0.6144188025420789</v>
+        <v>-0.614418802542079</v>
       </c>
     </row>
     <row r="28">
@@ -1108,16 +1108,16 @@
         <v>4.884567747061518</v>
       </c>
       <c r="D28">
-        <v>-0.3603057830185341</v>
+        <v>-0.3603057830185355</v>
       </c>
       <c r="E28">
-        <v>0.4690576408571516</v>
+        <v>0.469057640857152</v>
       </c>
       <c r="F28">
-        <v>0.1479570583845453</v>
+        <v>0.1479570583845452</v>
       </c>
       <c r="G28">
-        <v>0.1270473812437841</v>
+        <v>0.1270473812437825</v>
       </c>
     </row>
     <row r="29">
@@ -1135,16 +1135,16 @@
         <v>-1.529953658581734</v>
       </c>
       <c r="D29">
-        <v>-0.2895361448167639</v>
+        <v>-0.2895361448167674</v>
       </c>
       <c r="E29">
-        <v>-0.9418160101003997</v>
+        <v>-0.9418160101003994</v>
       </c>
       <c r="F29">
-        <v>0.3844348510941693</v>
+        <v>0.3844348510941709</v>
       </c>
       <c r="G29">
-        <v>-0.5909887372841613</v>
+        <v>-0.5909887372841618</v>
       </c>
     </row>
     <row r="30">
@@ -1162,16 +1162,16 @@
         <v>-1.703556887176861</v>
       </c>
       <c r="D30">
-        <v>0.4643507248186864</v>
+        <v>0.4643507248186836</v>
       </c>
       <c r="E30">
-        <v>0.02258679258667117</v>
+        <v>0.02258679258666776</v>
       </c>
       <c r="F30">
-        <v>-0.8746517642887672</v>
+        <v>-0.8746517642887677</v>
       </c>
       <c r="G30">
-        <v>-0.4264338894148011</v>
+        <v>-0.4264338894148014</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>-2.449563202741587</v>
+        <v>-2.449563202741588</v>
       </c>
       <c r="D31">
         <v>1.518113771439276</v>
       </c>
       <c r="E31">
-        <v>1.02271202544856</v>
+        <v>1.022712025448561</v>
       </c>
       <c r="F31">
-        <v>0.8219817061241412</v>
+        <v>0.8219817061241388</v>
       </c>
       <c r="G31">
-        <v>0.4657156816136901</v>
+        <v>0.465715681613691</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.4865622204254928</v>
+        <v>-0.486562220425493</v>
       </c>
       <c r="D32">
-        <v>0.4719789812281852</v>
+        <v>0.471978981228183</v>
       </c>
       <c r="E32">
-        <v>0.3602040894498724</v>
+        <v>0.3602040894498701</v>
       </c>
       <c r="F32">
-        <v>-0.4246173054864614</v>
+        <v>-0.4246173054864626</v>
       </c>
       <c r="G32">
-        <v>-0.1709851490050993</v>
+        <v>-0.1709851490051011</v>
       </c>
     </row>
     <row r="33">
@@ -1243,16 +1243,16 @@
         <v>2.144451863904631</v>
       </c>
       <c r="D33">
-        <v>-1.478267321307285</v>
+        <v>-1.478267321307288</v>
       </c>
       <c r="E33">
-        <v>0.01383932645733941</v>
+        <v>0.01383932645734337</v>
       </c>
       <c r="F33">
-        <v>1.180821717192834</v>
+        <v>1.180821717192835</v>
       </c>
       <c r="G33">
-        <v>-0.08036033579665849</v>
+        <v>-0.08036033579665912</v>
       </c>
     </row>
     <row r="34">
@@ -1270,16 +1270,16 @@
         <v>3.390968096912704</v>
       </c>
       <c r="D34">
-        <v>-0.3200048994524247</v>
+        <v>-0.320004899452427</v>
       </c>
       <c r="E34">
-        <v>0.3237291907405602</v>
+        <v>0.3237291907405571</v>
       </c>
       <c r="F34">
-        <v>-1.142889520931905</v>
+        <v>-1.142889520931906</v>
       </c>
       <c r="G34">
-        <v>-0.4837077311901133</v>
+        <v>-0.4837077311901148</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>1.642844128846516</v>
+        <v>1.642844128846515</v>
       </c>
       <c r="D35">
-        <v>0.908209891288168</v>
+        <v>0.9082098912881681</v>
       </c>
       <c r="E35">
-        <v>0.6562208734176249</v>
+        <v>0.6562208734176267</v>
       </c>
       <c r="F35">
-        <v>0.9760359662327028</v>
+        <v>0.9760359662327008</v>
       </c>
       <c r="G35">
-        <v>1.268713744429594</v>
+        <v>1.26871374442959</v>
       </c>
     </row>
     <row r="36">
@@ -1324,16 +1324,16 @@
         <v>-1.031389481834293</v>
       </c>
       <c r="D36">
-        <v>-2.316929528541634</v>
+        <v>-2.316929528541636</v>
       </c>
       <c r="E36">
-        <v>1.876290052374815</v>
+        <v>1.876290052374818</v>
       </c>
       <c r="F36">
-        <v>0.3275040049270392</v>
+        <v>0.3275040049270347</v>
       </c>
       <c r="G36">
-        <v>0.3393567483669157</v>
+        <v>0.3393567483669154</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.2639850309913557</v>
+        <v>0.2639850309913551</v>
       </c>
       <c r="D37">
-        <v>-2.221096755482493</v>
+        <v>-2.221096755482495</v>
       </c>
       <c r="E37">
-        <v>1.425426690531333</v>
+        <v>1.425426690531334</v>
       </c>
       <c r="F37">
-        <v>0.4715736500182095</v>
+        <v>0.4715736500182059</v>
       </c>
       <c r="G37">
-        <v>0.05880078052361801</v>
+        <v>0.05880078052361552</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.1947972026247036</v>
+        <v>0.1947972026247028</v>
       </c>
       <c r="D38">
         <v>1.029893649646467</v>
       </c>
       <c r="E38">
-        <v>2.09990119003824</v>
+        <v>2.099901190038242</v>
       </c>
       <c r="F38">
-        <v>0.7404014211951954</v>
+        <v>0.7404014211951897</v>
       </c>
       <c r="G38">
-        <v>0.04374056562167924</v>
+        <v>0.0437405656216768</v>
       </c>
     </row>
     <row r="39">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>-2.989473781489617</v>
+        <v>-2.989473781489618</v>
       </c>
       <c r="D39">
-        <v>0.8701697298408483</v>
+        <v>0.8701697298408463</v>
       </c>
       <c r="E39">
-        <v>0.6315368988714628</v>
+        <v>0.631536898871463</v>
       </c>
       <c r="F39">
-        <v>0.6714122688563443</v>
+        <v>0.6714122688563413</v>
       </c>
       <c r="G39">
-        <v>-0.6840893247965373</v>
+        <v>-0.6840893247965393</v>
       </c>
     </row>
     <row r="40">
@@ -1432,16 +1432,16 @@
         <v>-1.834543485978561</v>
       </c>
       <c r="D40">
-        <v>2.252340801476134</v>
+        <v>2.252340801476132</v>
       </c>
       <c r="E40">
-        <v>0.9834418768209187</v>
+        <v>0.9834418768209153</v>
       </c>
       <c r="F40">
-        <v>-0.3197232057366052</v>
+        <v>-0.3197232057366086</v>
       </c>
       <c r="G40">
-        <v>-0.7045046175729965</v>
+        <v>-0.7045046175729986</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.3012419289554674</v>
+        <v>0.3012419289554675</v>
       </c>
       <c r="D41">
-        <v>0.5198897205670193</v>
+        <v>0.5198897205670168</v>
       </c>
       <c r="E41">
-        <v>-0.4969207205794782</v>
+        <v>-0.4969207205794802</v>
       </c>
       <c r="F41">
-        <v>-0.4114947567592662</v>
+        <v>-0.4114947567592651</v>
       </c>
       <c r="G41">
-        <v>-0.2623754476657968</v>
+        <v>-0.2623754476657986</v>
       </c>
     </row>
     <row r="42">
@@ -1486,16 +1486,16 @@
         <v>4.7886877712356</v>
       </c>
       <c r="D42">
-        <v>-0.9566775171029379</v>
+        <v>-0.9566775171029396</v>
       </c>
       <c r="E42">
-        <v>0.6007385019444317</v>
+        <v>0.6007385019444316</v>
       </c>
       <c r="F42">
-        <v>-0.2153238800170084</v>
+        <v>-0.2153238800170091</v>
       </c>
       <c r="G42">
-        <v>0.121816722853128</v>
+        <v>0.1218167228531267</v>
       </c>
     </row>
     <row r="43">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>-5.302515264109022</v>
+        <v>-5.302515264109021</v>
       </c>
       <c r="D43">
-        <v>-3.550183306689093</v>
+        <v>-3.550183306689096</v>
       </c>
       <c r="E43">
-        <v>-0.7500938315780094</v>
+        <v>-0.7500938315780068</v>
       </c>
       <c r="F43">
-        <v>0.3186048847608713</v>
+        <v>0.3186048847608736</v>
       </c>
       <c r="G43">
-        <v>1.133230064303626</v>
+        <v>1.133230064303627</v>
       </c>
     </row>
     <row r="44">
@@ -1540,16 +1540,16 @@
         <v>2.005840763306023</v>
       </c>
       <c r="D44">
-        <v>-1.675982457807871</v>
+        <v>-1.675982457807874</v>
       </c>
       <c r="E44">
-        <v>-0.06608446659638727</v>
+        <v>-0.06608446659638513</v>
       </c>
       <c r="F44">
-        <v>0.4858667823767774</v>
+        <v>0.4858667823767783</v>
       </c>
       <c r="G44">
-        <v>-0.1716483906805166</v>
+        <v>-0.1716483906805169</v>
       </c>
     </row>
     <row r="45">
@@ -1567,16 +1567,16 @@
         <v>-2.50366876617582</v>
       </c>
       <c r="D45">
-        <v>1.206026262996198</v>
+        <v>1.206026262996196</v>
       </c>
       <c r="E45">
-        <v>-0.6124199467938123</v>
+        <v>-0.6124199467938167</v>
       </c>
       <c r="F45">
-        <v>-0.9838770196536796</v>
+        <v>-0.9838770196536786</v>
       </c>
       <c r="G45">
-        <v>0.2994681773829536</v>
+        <v>0.2994681773829531</v>
       </c>
     </row>
     <row r="46">
@@ -1594,16 +1594,16 @@
         <v>-2.126571811842205</v>
       </c>
       <c r="D46">
-        <v>-0.4494359026634916</v>
+        <v>-0.4494359026634935</v>
       </c>
       <c r="E46">
-        <v>1.288945642500676</v>
+        <v>1.288945642500677</v>
       </c>
       <c r="F46">
-        <v>0.2526650283259207</v>
+        <v>0.2526650283259168</v>
       </c>
       <c r="G46">
-        <v>-0.2148308235501411</v>
+        <v>-0.2148308235501427</v>
       </c>
     </row>
     <row r="47">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>3.010103377546382</v>
+        <v>3.010103377546383</v>
       </c>
       <c r="D47">
-        <v>0.03489070196765908</v>
+        <v>0.03489070196765703</v>
       </c>
       <c r="E47">
-        <v>-0.5315307180228097</v>
+        <v>-0.5315307180228103</v>
       </c>
       <c r="F47">
-        <v>-0.1670836439781646</v>
+        <v>-0.1670836439781622</v>
       </c>
       <c r="G47">
-        <v>-0.1176680662899455</v>
+        <v>-0.1176680662899448</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>4.881696161925493</v>
+        <v>4.881696161925492</v>
       </c>
       <c r="D48">
-        <v>0.8095677407056383</v>
+        <v>0.8095677407056385</v>
       </c>
       <c r="E48">
-        <v>1.574738367596623</v>
+        <v>1.574738367596622</v>
       </c>
       <c r="F48">
-        <v>0.2533743785005247</v>
+        <v>0.253374378500521</v>
       </c>
       <c r="G48">
-        <v>0.1302440230940316</v>
+        <v>0.1302440230940285</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.08783897297245928</v>
+        <v>-0.08783897297245909</v>
       </c>
       <c r="D49">
-        <v>0.7020782653663475</v>
+        <v>0.7020782653663458</v>
       </c>
       <c r="E49">
-        <v>-0.4306079624623431</v>
+        <v>-0.4306079624623466</v>
       </c>
       <c r="F49">
-        <v>-0.9467363895614026</v>
+        <v>-0.9467363895614012</v>
       </c>
       <c r="G49">
-        <v>-0.02883941748263818</v>
+        <v>-0.02883941748263798</v>
       </c>
     </row>
     <row r="50">
@@ -1702,16 +1702,16 @@
         <v>-3.662552669358568</v>
       </c>
       <c r="D50">
-        <v>-1.036389359990229</v>
+        <v>-1.036389359990231</v>
       </c>
       <c r="E50">
-        <v>0.5945798967869202</v>
+        <v>0.5945798967869171</v>
       </c>
       <c r="F50">
-        <v>-1.130289553235418</v>
+        <v>-1.13028955323542</v>
       </c>
       <c r="G50">
-        <v>0.3069546972944246</v>
+        <v>0.3069546972944241</v>
       </c>
     </row>
     <row r="51">
@@ -1729,16 +1729,16 @@
         <v>-1.188621762817268</v>
       </c>
       <c r="D51">
-        <v>-0.5085543255714428</v>
+        <v>-0.508554325571446</v>
       </c>
       <c r="E51">
-        <v>-0.296320925759386</v>
+        <v>-0.2963209257593871</v>
       </c>
       <c r="F51">
-        <v>-0.315190905065264</v>
+        <v>-0.3151909050652632</v>
       </c>
       <c r="G51">
-        <v>-0.6782762723373809</v>
+        <v>-0.6782762723373797</v>
       </c>
     </row>
     <row r="52">
@@ -1756,16 +1756,16 @@
         <v>4.395315528383128</v>
       </c>
       <c r="D52">
-        <v>-0.6076773251700009</v>
+        <v>-0.6076773251700038</v>
       </c>
       <c r="E52">
-        <v>-0.5153515505858632</v>
+        <v>-0.515351550585864</v>
       </c>
       <c r="F52">
-        <v>-0.3870668902466081</v>
+        <v>-0.3870668902466058</v>
       </c>
       <c r="G52">
-        <v>-0.2463300861272623</v>
+        <v>-0.2463300861272634</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>-0.8470709494380315</v>
+        <v>-0.8470709494380317</v>
       </c>
       <c r="D53">
-        <v>0.2225998249551871</v>
+        <v>0.2225998249551854</v>
       </c>
       <c r="E53">
-        <v>0.4487334767171465</v>
+        <v>0.4487334767171457</v>
       </c>
       <c r="F53">
-        <v>0.02442230238486945</v>
+        <v>0.02442230238486798</v>
       </c>
       <c r="G53">
-        <v>0.107690294455351</v>
+        <v>0.1076902944553499</v>
       </c>
     </row>
     <row r="54">
@@ -1810,16 +1810,16 @@
         <v>-4.311279051475724</v>
       </c>
       <c r="D54">
-        <v>1.375870383874149</v>
+        <v>1.375870383874148</v>
       </c>
       <c r="E54">
-        <v>0.7267423664398098</v>
+        <v>0.7267423664398142</v>
       </c>
       <c r="F54">
-        <v>2.484194974604169</v>
+        <v>2.484194974604165</v>
       </c>
       <c r="G54">
-        <v>-0.003488968041432734</v>
+        <v>-0.003488968041435652</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>1.174009274764125</v>
+        <v>1.174009274764126</v>
       </c>
       <c r="D55">
-        <v>-0.5283424605177234</v>
+        <v>-0.5283424605177266</v>
       </c>
       <c r="E55">
         <v>-1.182072866487093</v>
       </c>
       <c r="F55">
-        <v>-0.0865424142244433</v>
+        <v>-0.08654241422444034</v>
       </c>
       <c r="G55">
-        <v>-0.02703669419367784</v>
+        <v>-0.0270366941936788</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>2.97182032201697</v>
+        <v>2.971820322016971</v>
       </c>
       <c r="D56">
-        <v>-0.440057161016614</v>
+        <v>-0.4400571610166176</v>
       </c>
       <c r="E56">
-        <v>-1.307533572225644</v>
+        <v>-1.307533572225646</v>
       </c>
       <c r="F56">
-        <v>-0.7733166874457302</v>
+        <v>-0.7733166874457265</v>
       </c>
       <c r="G56">
-        <v>-0.3854935368438167</v>
+        <v>-0.3854935368438175</v>
       </c>
     </row>
     <row r="57">
@@ -1891,16 +1891,16 @@
         <v>1.853067533489188</v>
       </c>
       <c r="D57">
-        <v>0.8133241220233854</v>
+        <v>0.8133241220233837</v>
       </c>
       <c r="E57">
-        <v>1.096859385966039</v>
+        <v>1.096859385966036</v>
       </c>
       <c r="F57">
-        <v>-0.4005317131053659</v>
+        <v>-0.4005317131053685</v>
       </c>
       <c r="G57">
-        <v>-0.7288066061578709</v>
+        <v>-0.7288066061578727</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>-0.1696426552909302</v>
+        <v>-0.1696426552909303</v>
       </c>
       <c r="D58">
-        <v>1.417806489961974</v>
+        <v>1.417806489961972</v>
       </c>
       <c r="E58">
-        <v>0.4660481251096597</v>
+        <v>0.4660481251096559</v>
       </c>
       <c r="F58">
-        <v>-0.805472521829805</v>
+        <v>-0.8054725218298059</v>
       </c>
       <c r="G58">
-        <v>-0.2953164637568915</v>
+        <v>-0.2953164637568916</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>-0.5522848015302174</v>
+        <v>-0.5522848015302178</v>
       </c>
       <c r="D59">
-        <v>0.7955264479133528</v>
+        <v>0.7955264479133519</v>
       </c>
       <c r="E59">
-        <v>1.207532573654656</v>
+        <v>1.207532573654654</v>
       </c>
       <c r="F59">
-        <v>-0.2999785618224166</v>
+        <v>-0.2999785618224195</v>
       </c>
       <c r="G59">
-        <v>0.22617483763611</v>
+        <v>0.2261748376361097</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>5.4782252225969</v>
+        <v>5.478225222596899</v>
       </c>
       <c r="D60">
-        <v>-0.303825771075204</v>
+        <v>-0.3038257710752044</v>
       </c>
       <c r="E60">
-        <v>0.8010079193873297</v>
+        <v>0.8010079193873307</v>
       </c>
       <c r="F60">
-        <v>0.3669297371464456</v>
+        <v>0.3669297371464445</v>
       </c>
       <c r="G60">
-        <v>0.374021403245565</v>
+        <v>0.3740214032455629</v>
       </c>
     </row>
     <row r="61">
@@ -1999,16 +1999,16 @@
         <v>2.934718185440324</v>
       </c>
       <c r="D61">
-        <v>1.412106421886043</v>
+        <v>1.412106421886041</v>
       </c>
       <c r="E61">
         <v>-2.296107753245937</v>
       </c>
       <c r="F61">
-        <v>0.5358379598286999</v>
+        <v>0.5358379598287079</v>
       </c>
       <c r="G61">
-        <v>0.5995253879641087</v>
+        <v>0.5995253879641139</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>-0.3845855668137916</v>
+        <v>-0.3845855668137919</v>
       </c>
       <c r="D62">
         <v>2.13339432024107</v>
       </c>
       <c r="E62">
-        <v>0.962602630329934</v>
+        <v>0.9626026303299311</v>
       </c>
       <c r="F62">
-        <v>-0.3189250312233867</v>
+        <v>-0.3189250312233894</v>
       </c>
       <c r="G62">
-        <v>0.06064179135726731</v>
+        <v>0.06064179135726631</v>
       </c>
     </row>
     <row r="63">
@@ -2050,19 +2050,19 @@
         </is>
       </c>
       <c r="C63">
-        <v>-0.6847251387078644</v>
+        <v>-0.6847251387078646</v>
       </c>
       <c r="D63">
         <v>2.043793295436565</v>
       </c>
       <c r="E63">
-        <v>1.151183177919539</v>
+        <v>1.151183177919536</v>
       </c>
       <c r="F63">
-        <v>-0.2994060998505803</v>
+        <v>-0.2994060998505834</v>
       </c>
       <c r="G63">
-        <v>0.2234000436174871</v>
+        <v>0.2234000436174862</v>
       </c>
     </row>
     <row r="64">
@@ -2080,16 +2080,16 @@
         <v>3.608837272879452</v>
       </c>
       <c r="D64">
-        <v>-0.437388029295907</v>
+        <v>-0.4373880292959078</v>
       </c>
       <c r="E64">
-        <v>1.340529720084787</v>
+        <v>1.340529720084786</v>
       </c>
       <c r="F64">
-        <v>-0.3150452923652976</v>
+        <v>-0.3150452923653001</v>
       </c>
       <c r="G64">
-        <v>0.1368557303577974</v>
+        <v>0.1368557303577959</v>
       </c>
     </row>
     <row r="65">
@@ -2107,16 +2107,16 @@
         <v>5.871974258057973</v>
       </c>
       <c r="D65">
-        <v>-0.05631899481841136</v>
+        <v>-0.0563189948184124</v>
       </c>
       <c r="E65">
-        <v>0.6551866817569982</v>
+        <v>0.655186681756999</v>
       </c>
       <c r="F65">
-        <v>0.2609362077502433</v>
+        <v>0.2609362077502426</v>
       </c>
       <c r="G65">
-        <v>-0.051992399450444</v>
+        <v>-0.05199239945044641</v>
       </c>
     </row>
     <row r="66">
@@ -2134,16 +2134,16 @@
         <v>4.587618389602309</v>
       </c>
       <c r="D66">
-        <v>-0.5543614722584411</v>
+        <v>-0.5543614722584422</v>
       </c>
       <c r="E66">
-        <v>1.003918531897937</v>
+        <v>1.003918531897938</v>
       </c>
       <c r="F66">
-        <v>0.4940024889158651</v>
+        <v>0.494002488915863</v>
       </c>
       <c r="G66">
-        <v>-0.1408195894440012</v>
+        <v>-0.140819589444004</v>
       </c>
     </row>
     <row r="67">
@@ -2161,16 +2161,16 @@
         <v>2.683343954160128</v>
       </c>
       <c r="D67">
-        <v>-1.020010999045637</v>
+        <v>-1.020010999045639</v>
       </c>
       <c r="E67">
-        <v>-0.4617728825337201</v>
+        <v>-0.4617728825337181</v>
       </c>
       <c r="F67">
-        <v>0.5434212422960774</v>
+        <v>0.5434212422960794</v>
       </c>
       <c r="G67">
-        <v>0.2201398507331941</v>
+        <v>0.2201398507331936</v>
       </c>
     </row>
     <row r="68">
@@ -2188,16 +2188,16 @@
         <v>-1.597768692016083</v>
       </c>
       <c r="D68">
-        <v>1.002788776814348</v>
+        <v>1.002788776814345</v>
       </c>
       <c r="E68">
-        <v>-0.5498723997956497</v>
+        <v>-0.5498723997956534</v>
       </c>
       <c r="F68">
-        <v>-0.8687402229200654</v>
+        <v>-0.8687402229200641</v>
       </c>
       <c r="G68">
-        <v>-0.2254281854168133</v>
+        <v>-0.2254281854168134</v>
       </c>
     </row>
     <row r="69">
@@ -2215,16 +2215,16 @@
         <v>-2.368275404080549</v>
       </c>
       <c r="D69">
-        <v>0.6212052605883993</v>
+        <v>0.6212052605883974</v>
       </c>
       <c r="E69">
-        <v>-0.09491062418358764</v>
+        <v>-0.09491062418358835</v>
       </c>
       <c r="F69">
-        <v>0.2005857958210213</v>
+        <v>0.200585795821021</v>
       </c>
       <c r="G69">
-        <v>0.3836045193186725</v>
+        <v>0.3836045193186711</v>
       </c>
     </row>
     <row r="70">
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>3.195012753258873</v>
+        <v>3.195012753258874</v>
       </c>
       <c r="D70">
-        <v>-0.7436600388816923</v>
+        <v>-0.7436600388816943</v>
       </c>
       <c r="E70">
-        <v>0.5178616546908013</v>
+        <v>0.5178616546908007</v>
       </c>
       <c r="F70">
-        <v>-0.2302217874233802</v>
+        <v>-0.2302217874233808</v>
       </c>
       <c r="G70">
-        <v>-0.2040907867650227</v>
+        <v>-0.2040907867650248</v>
       </c>
     </row>
     <row r="71">
@@ -2269,16 +2269,16 @@
         <v>-2.731272184699783</v>
       </c>
       <c r="D71">
-        <v>1.418265124769825</v>
+        <v>1.418265124769823</v>
       </c>
       <c r="E71">
-        <v>-0.1210390736267007</v>
+        <v>-0.1210390736267031</v>
       </c>
       <c r="F71">
-        <v>-0.2002066447901872</v>
+        <v>-0.2002066447901876</v>
       </c>
       <c r="G71">
-        <v>-0.01906317501662964</v>
+        <v>-0.01906317501662966</v>
       </c>
     </row>
     <row r="72">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-9.578007198210489</v>
+        <v>-9.578007198210488</v>
       </c>
       <c r="D72">
-        <v>-4.899204684115723</v>
+        <v>-4.899204684115729</v>
       </c>
       <c r="E72">
-        <v>1.261653038191755</v>
+        <v>1.261653038191749</v>
       </c>
       <c r="F72">
-        <v>-3.178647218392344</v>
+        <v>-3.178647218392348</v>
       </c>
       <c r="G72">
-        <v>0.2529521662454002</v>
+        <v>0.2529521662454017</v>
       </c>
     </row>
     <row r="73">
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-2.704709332071609</v>
+        <v>-2.704709332071608</v>
       </c>
       <c r="D73">
-        <v>-2.409743377638899</v>
+        <v>-2.409743377638903</v>
       </c>
       <c r="E73">
-        <v>-0.5514128313330376</v>
+        <v>-0.5514128313330371</v>
       </c>
       <c r="F73">
-        <v>-0.2733840361594128</v>
+        <v>-0.2733840361594115</v>
       </c>
       <c r="G73">
-        <v>-0.1981874315238859</v>
+        <v>-0.198187431523885</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>-3.952563759578498</v>
+        <v>-3.952563759578499</v>
       </c>
       <c r="D74">
-        <v>1.601169722619971</v>
+        <v>1.601169722619969</v>
       </c>
       <c r="E74">
         <v>0.1364965771960494</v>
       </c>
       <c r="F74">
-        <v>0.8539100520351262</v>
+        <v>0.8539100520351244</v>
       </c>
       <c r="G74">
-        <v>-0.4600992432300504</v>
+        <v>-0.460099243230052</v>
       </c>
     </row>
     <row r="75">
@@ -2377,16 +2377,16 @@
         <v>-2.601625061460636</v>
       </c>
       <c r="D75">
-        <v>-2.40640097870009</v>
+        <v>-2.406400978700094</v>
       </c>
       <c r="E75">
-        <v>-1.468264576832685</v>
+        <v>-1.468264576832683</v>
       </c>
       <c r="F75">
-        <v>0.2690065332859889</v>
+        <v>0.2690065332859917</v>
       </c>
       <c r="G75">
-        <v>-0.04798937109805451</v>
+        <v>-0.04798937109805509</v>
       </c>
     </row>
     <row r="76">
@@ -2404,16 +2404,16 @@
         <v>-3.778390279481148</v>
       </c>
       <c r="D76">
-        <v>-0.5634146065020073</v>
+        <v>-0.5634146065020091</v>
       </c>
       <c r="E76">
-        <v>0.6030927118256998</v>
+        <v>0.6030927118257008</v>
       </c>
       <c r="F76">
-        <v>0.4828889961167754</v>
+        <v>0.4828889961167734</v>
       </c>
       <c r="G76">
-        <v>0.3383907359783653</v>
+        <v>0.3383907359783647</v>
       </c>
     </row>
     <row r="77">
@@ -2431,16 +2431,16 @@
         <v>-3.154148551084579</v>
       </c>
       <c r="D77">
-        <v>3.584603224275532</v>
+        <v>3.584603224275531</v>
       </c>
       <c r="E77">
-        <v>-0.8175870056166724</v>
+        <v>-0.8175870056166787</v>
       </c>
       <c r="F77">
-        <v>-1.556186215513771</v>
+        <v>-1.556186215513769</v>
       </c>
       <c r="G77">
-        <v>2.721641227633429</v>
+        <v>2.721641227633426</v>
       </c>
     </row>
     <row r="78">
@@ -2458,16 +2458,16 @@
         <v>0.2646119637803071</v>
       </c>
       <c r="D78">
-        <v>0.2059351114495118</v>
+        <v>0.2059351114495099</v>
       </c>
       <c r="E78">
-        <v>0.4760064502525999</v>
+        <v>0.4760064502525981</v>
       </c>
       <c r="F78">
-        <v>-0.4501528952603996</v>
+        <v>-0.4501528952604006</v>
       </c>
       <c r="G78">
-        <v>-0.2454420245632171</v>
+        <v>-0.2454420245632175</v>
       </c>
     </row>
     <row r="79">
@@ -2485,16 +2485,16 @@
         <v>-1.815392039459216</v>
       </c>
       <c r="D79">
-        <v>-0.3422622962597872</v>
+        <v>-0.3422622962597904</v>
       </c>
       <c r="E79">
-        <v>-0.3462516531023884</v>
+        <v>-0.346251653102392</v>
       </c>
       <c r="F79">
-        <v>-1.108387078644779</v>
+        <v>-1.108387078644778</v>
       </c>
       <c r="G79">
-        <v>-0.2776096667747821</v>
+        <v>-0.2776096667747822</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>-1.806067802101922</v>
+        <v>-1.806067802101923</v>
       </c>
       <c r="D80">
-        <v>0.8256237084149671</v>
+        <v>0.8256237084149656</v>
       </c>
       <c r="E80">
-        <v>1.158406119573392</v>
+        <v>1.158406119573389</v>
       </c>
       <c r="F80">
-        <v>-0.5244424622569916</v>
+        <v>-0.524442462256995</v>
       </c>
       <c r="G80">
-        <v>-0.2717012050966252</v>
+        <v>-0.2717012050966272</v>
       </c>
     </row>
     <row r="81">
@@ -2539,16 +2539,16 @@
         <v>2.790200775526104</v>
       </c>
       <c r="D81">
-        <v>-0.2064538252666024</v>
+        <v>-0.2064538252666029</v>
       </c>
       <c r="E81">
-        <v>0.464686141174337</v>
+        <v>0.4646861411743409</v>
       </c>
       <c r="F81">
         <v>1.597678231547657</v>
       </c>
       <c r="G81">
-        <v>0.516933045215495</v>
+        <v>0.5169330452154949</v>
       </c>
     </row>
     <row r="82">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.2700342082490949</v>
+        <v>0.2700342082490951</v>
       </c>
       <c r="D82">
-        <v>1.143744810013357</v>
+        <v>1.143744810013354</v>
       </c>
       <c r="E82">
-        <v>-0.2450385781996396</v>
+        <v>-0.2450385781996435</v>
       </c>
       <c r="F82">
-        <v>-0.8495403638172832</v>
+        <v>-0.8495403638172825</v>
       </c>
       <c r="G82">
-        <v>-0.5472226500043613</v>
+        <v>-0.5472226500043624</v>
       </c>
     </row>
     <row r="83">
@@ -2593,16 +2593,16 @@
         <v>3.213218459992567</v>
       </c>
       <c r="D83">
-        <v>0.7158294018000816</v>
+        <v>0.7158294018000784</v>
       </c>
       <c r="E83">
         <v>-2.589470703510568</v>
       </c>
       <c r="F83">
-        <v>0.3014114837722186</v>
+        <v>0.301411483772226</v>
       </c>
       <c r="G83">
-        <v>-0.3454502494606739</v>
+        <v>-0.3454502494606716</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>0.8801814934219009</v>
+        <v>0.880181493421901</v>
       </c>
       <c r="D84">
-        <v>-0.6555920694158187</v>
+        <v>-0.655592069415822</v>
       </c>
       <c r="E84">
-        <v>-0.588838834286834</v>
+        <v>-0.5888388342868347</v>
       </c>
       <c r="F84">
-        <v>-0.1082900689597991</v>
+        <v>-0.1082900689597977</v>
       </c>
       <c r="G84">
-        <v>-0.3748842257802726</v>
+        <v>-0.3748842257802742</v>
       </c>
     </row>
     <row r="85">
@@ -2647,16 +2647,16 @@
         <v>2.685365047552287</v>
       </c>
       <c r="D85">
-        <v>0.6220219853143435</v>
+        <v>0.6220219853143415</v>
       </c>
       <c r="E85">
-        <v>0.3017445549515763</v>
+        <v>0.3017445549515729</v>
       </c>
       <c r="F85">
-        <v>-0.9714700977744908</v>
+        <v>-0.9714700977744911</v>
       </c>
       <c r="G85">
-        <v>-0.2783202502864267</v>
+        <v>-0.2783202502864282</v>
       </c>
     </row>
     <row r="86">
@@ -2674,16 +2674,16 @@
         <v>4.393008264395985</v>
       </c>
       <c r="D86">
-        <v>-0.4604690636649056</v>
+        <v>-0.4604690636649075</v>
       </c>
       <c r="E86">
-        <v>-0.614655261626697</v>
+        <v>-0.6146552616266958</v>
       </c>
       <c r="F86">
-        <v>0.3170815840060416</v>
+        <v>0.3170815840060442</v>
       </c>
       <c r="G86">
-        <v>0.2868353421101782</v>
+        <v>0.2868353421101775</v>
       </c>
     </row>
     <row r="87">
@@ -2701,16 +2701,16 @@
         <v>-2.03383529909697</v>
       </c>
       <c r="D87">
-        <v>0.9652044815825483</v>
+        <v>0.9652044815825469</v>
       </c>
       <c r="E87">
-        <v>-0.4689712971853243</v>
+        <v>-0.468971297185325</v>
       </c>
       <c r="F87">
-        <v>0.06787709261707499</v>
+        <v>0.06787709261707603</v>
       </c>
       <c r="G87">
-        <v>0.6290501036450982</v>
+        <v>0.6290501036450989</v>
       </c>
     </row>
     <row r="88">
@@ -2728,16 +2728,16 @@
         <v>6.450568906685234</v>
       </c>
       <c r="D88">
-        <v>-0.1381233720380202</v>
+        <v>-0.1381233720380211</v>
       </c>
       <c r="E88">
-        <v>0.9160870382643725</v>
+        <v>0.9160870382643715</v>
       </c>
       <c r="F88">
-        <v>-0.3654246469937591</v>
+        <v>-0.3654246469937599</v>
       </c>
       <c r="G88">
-        <v>-0.2793870261717821</v>
+        <v>-0.2793870261717841</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.7366454005806014</v>
+        <v>0.7366454005806015</v>
       </c>
       <c r="D89">
-        <v>0.5430356908053641</v>
+        <v>0.5430356908053618</v>
       </c>
       <c r="E89">
-        <v>-0.3485586867403435</v>
+        <v>-0.3485586867403467</v>
       </c>
       <c r="F89">
-        <v>-0.828467472854439</v>
+        <v>-0.8284674728544383</v>
       </c>
       <c r="G89">
-        <v>0.06759103426220212</v>
+        <v>0.06759103426220082</v>
       </c>
     </row>
     <row r="90">
@@ -2782,16 +2782,16 @@
         <v>-1.347067451690338</v>
       </c>
       <c r="D90">
-        <v>-0.323678221421534</v>
+        <v>-0.3236782214215368</v>
       </c>
       <c r="E90">
-        <v>-0.12856555141997</v>
+        <v>-0.128565551419971</v>
       </c>
       <c r="F90">
-        <v>-0.2209984420004729</v>
+        <v>-0.2209984420004726</v>
       </c>
       <c r="G90">
-        <v>-0.2901732618840391</v>
+        <v>-0.2901732618840387</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>-1.768146128028688</v>
+        <v>-1.768146128028689</v>
       </c>
       <c r="D91">
-        <v>0.9345355094637952</v>
+        <v>0.9345355094637934</v>
       </c>
       <c r="E91">
-        <v>0.047143115779649</v>
+        <v>0.04714311577964995</v>
       </c>
       <c r="F91">
-        <v>0.8858444520853441</v>
+        <v>0.8858444520853432</v>
       </c>
       <c r="G91">
-        <v>0.03136119524861641</v>
+        <v>0.03136119524861569</v>
       </c>
     </row>
     <row r="92">
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>-5.991509776497614</v>
+        <v>-5.991509776497615</v>
       </c>
       <c r="D92">
-        <v>1.66020137658351</v>
+        <v>1.660201376583509</v>
       </c>
       <c r="E92">
-        <v>1.180917746355157</v>
+        <v>1.180917746355159</v>
       </c>
       <c r="F92">
-        <v>1.784641655689816</v>
+        <v>1.784641655689811</v>
       </c>
       <c r="G92">
-        <v>-1.140418324509938</v>
+        <v>-1.14041832450994</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>2.281744212005263</v>
+        <v>2.281744212005264</v>
       </c>
       <c r="D93">
-        <v>-0.2013788603489793</v>
+        <v>-0.201378860348982</v>
       </c>
       <c r="E93">
-        <v>-0.2928136475457253</v>
+        <v>-0.292813647545729</v>
       </c>
       <c r="F93">
-        <v>-1.33110643574323</v>
+        <v>-1.331106435743228</v>
       </c>
       <c r="G93">
-        <v>-0.1678455778014462</v>
+        <v>-0.1678455778014465</v>
       </c>
     </row>
     <row r="94">
@@ -2890,16 +2890,16 @@
         <v>1.410879522724387</v>
       </c>
       <c r="D94">
-        <v>0.819542983608098</v>
+        <v>0.8195429836080984</v>
       </c>
       <c r="E94">
-        <v>-0.2767888355908453</v>
+        <v>-0.2767888355908434</v>
       </c>
       <c r="F94">
-        <v>0.8374094740237998</v>
+        <v>0.8374094740238023</v>
       </c>
       <c r="G94">
-        <v>1.250768349707873</v>
+        <v>1.250768349707877</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-3.803107770429491</v>
+        <v>-3.803107770429492</v>
       </c>
       <c r="D95">
-        <v>-1.407922717132298</v>
+        <v>-1.407922717132302</v>
       </c>
       <c r="E95">
-        <v>-0.8535509096121865</v>
+        <v>-0.8535509096121838</v>
       </c>
       <c r="F95">
         <v>1.187155727197519</v>
       </c>
       <c r="G95">
-        <v>0.02119526105070406</v>
+        <v>0.02119526105070284</v>
       </c>
     </row>
     <row r="96">
@@ -2944,16 +2944,16 @@
         <v>-1.851945096425885</v>
       </c>
       <c r="D96">
-        <v>0.1063150080047301</v>
+        <v>0.106315008004729</v>
       </c>
       <c r="E96">
-        <v>0.6425699166047852</v>
+        <v>0.6425699166047867</v>
       </c>
       <c r="F96">
-        <v>0.8023681880588114</v>
+        <v>0.8023681880588093</v>
       </c>
       <c r="G96">
-        <v>0.3841249990843741</v>
+        <v>0.3841249990843728</v>
       </c>
     </row>
     <row r="97">
@@ -2968,19 +2968,19 @@
         </is>
       </c>
       <c r="C97">
-        <v>3.519867738187843</v>
+        <v>3.519867738187842</v>
       </c>
       <c r="D97">
-        <v>-0.8525423396535208</v>
+        <v>-0.8525423396535234</v>
       </c>
       <c r="E97">
-        <v>-0.2105188039531006</v>
+        <v>-0.2105188039531021</v>
       </c>
       <c r="F97">
-        <v>-0.6842529404481641</v>
+        <v>-0.6842529404481626</v>
       </c>
       <c r="G97">
-        <v>-0.4527804008644064</v>
+        <v>-0.4527804008644071</v>
       </c>
     </row>
     <row r="98">
@@ -2998,16 +2998,16 @@
         <v>-1.304153095108601</v>
       </c>
       <c r="D98">
-        <v>-1.562099254655729</v>
+        <v>-1.562099254655732</v>
       </c>
       <c r="E98">
-        <v>-0.7639768341097626</v>
+        <v>-0.7639768341097607</v>
       </c>
       <c r="F98">
-        <v>0.4877281653932492</v>
+        <v>0.4877281653932505</v>
       </c>
       <c r="G98">
-        <v>0.4267119117012151</v>
+        <v>0.4267119117012139</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>-0.7825085724448266</v>
+        <v>-0.7825085724448269</v>
       </c>
       <c r="D99">
-        <v>-0.2066489495018837</v>
+        <v>-0.2066489495018859</v>
       </c>
       <c r="E99">
-        <v>0.2072637954250754</v>
+        <v>0.2072637954250751</v>
       </c>
       <c r="F99">
-        <v>0.1357244000789982</v>
+        <v>0.1357244000789972</v>
       </c>
       <c r="G99">
-        <v>-0.04440460122915642</v>
+        <v>-0.04440460122915788</v>
       </c>
     </row>
     <row r="100">
@@ -3052,16 +3052,16 @@
         <v>-0.7062888805419928</v>
       </c>
       <c r="D100">
-        <v>0.651745261821427</v>
+        <v>0.6517452618214247</v>
       </c>
       <c r="E100">
         <v>-0.9037445169812106</v>
       </c>
       <c r="F100">
-        <v>0.4203544148147965</v>
+        <v>0.4203544148147982</v>
       </c>
       <c r="G100">
-        <v>0.1355397827048731</v>
+        <v>0.1355397827048723</v>
       </c>
     </row>
     <row r="101">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C101">
-        <v>1.128271095946631</v>
+        <v>1.128271095946632</v>
       </c>
       <c r="D101">
-        <v>0.5386942876295003</v>
+        <v>0.5386942876294971</v>
       </c>
       <c r="E101">
-        <v>-1.202147921709408</v>
+        <v>-1.20214792170941</v>
       </c>
       <c r="F101">
-        <v>-0.4970063469383184</v>
+        <v>-0.4970063469383149</v>
       </c>
       <c r="G101">
-        <v>-0.4342969719467339</v>
+        <v>-0.4342969719467337</v>
       </c>
     </row>
     <row r="102">
@@ -3106,16 +3106,16 @@
         <v>-0.7392868749297257</v>
       </c>
       <c r="D102">
-        <v>0.298082784203256</v>
+        <v>0.2980827842032542</v>
       </c>
       <c r="E102">
-        <v>0.7402028344930902</v>
+        <v>0.7402028344930854</v>
       </c>
       <c r="F102">
-        <v>-1.46600556803012</v>
+        <v>-1.466005568030122</v>
       </c>
       <c r="G102">
-        <v>-0.09292019701558046</v>
+        <v>-0.09292019701558198</v>
       </c>
     </row>
     <row r="103">
@@ -3133,16 +3133,16 @@
         <v>2.775589185924864</v>
       </c>
       <c r="D103">
-        <v>-0.904962319755329</v>
+        <v>-0.9049623197553318</v>
       </c>
       <c r="E103">
-        <v>-0.3161472802322476</v>
+        <v>-0.3161472802322481</v>
       </c>
       <c r="F103">
-        <v>-0.3104766686935201</v>
+        <v>-0.3104766686935186</v>
       </c>
       <c r="G103">
-        <v>-0.07151081442865924</v>
+        <v>-0.07151081442865956</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>-0.4620083382769546</v>
+        <v>-0.4620083382769544</v>
       </c>
       <c r="D104">
-        <v>0.3028087250325833</v>
+        <v>0.3028087250325808</v>
       </c>
       <c r="E104">
-        <v>-1.528246049315147</v>
+        <v>-1.528246049315149</v>
       </c>
       <c r="F104">
-        <v>-0.4575252359504022</v>
+        <v>-0.4575252359503982</v>
       </c>
       <c r="G104">
-        <v>1.155232768680541</v>
+        <v>1.15523276868054</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>-0.951227018880571</v>
+        <v>-0.9512270188805716</v>
       </c>
       <c r="D105">
-        <v>-0.2752277521577031</v>
+        <v>-0.2752277521577045</v>
       </c>
       <c r="E105">
-        <v>1.23440492493729</v>
+        <v>1.234404924937292</v>
       </c>
       <c r="F105">
-        <v>0.6920312368407256</v>
+        <v>0.6920312368407219</v>
       </c>
       <c r="G105">
-        <v>-0.00428750122645674</v>
+        <v>-0.004287501226458369</v>
       </c>
     </row>
     <row r="106">
@@ -3214,16 +3214,16 @@
         <v>1.921846992658691</v>
       </c>
       <c r="D106">
-        <v>-1.674442282874896</v>
+        <v>-1.674442282874897</v>
       </c>
       <c r="E106">
         <v>1.037707194579489</v>
       </c>
       <c r="F106">
-        <v>0.01611206078961389</v>
+        <v>0.0161120607896118</v>
       </c>
       <c r="G106">
-        <v>0.3598461308902915</v>
+        <v>0.35984613089029</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.5163864860657216</v>
+        <v>0.5163864860657215</v>
       </c>
       <c r="D107">
-        <v>0.04702309913431108</v>
+        <v>0.04702309913430942</v>
       </c>
       <c r="E107">
-        <v>-0.6672488545044941</v>
+        <v>-0.6672488545044925</v>
       </c>
       <c r="F107">
-        <v>0.6889995819353042</v>
+        <v>0.6889995819353061</v>
       </c>
       <c r="G107">
-        <v>0.6355317471241607</v>
+        <v>0.6355317471241602</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.6019322654057837</v>
+        <v>0.6019322654057836</v>
       </c>
       <c r="D108">
-        <v>-0.2606008636485533</v>
+        <v>-0.2606008636485553</v>
       </c>
       <c r="E108">
-        <v>-0.6077144475789941</v>
+        <v>-0.6077144475789952</v>
       </c>
       <c r="F108">
-        <v>-0.4865575847117246</v>
+        <v>-0.4865575847117223</v>
       </c>
       <c r="G108">
-        <v>0.7078184670414079</v>
+        <v>0.7078184670414085</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.7423160942250068</v>
+        <v>-0.742316094225007</v>
       </c>
       <c r="D109">
-        <v>1.116936789820242</v>
+        <v>1.11693678982024</v>
       </c>
       <c r="E109">
-        <v>0.4589955654586699</v>
+        <v>0.4589955654586667</v>
       </c>
       <c r="F109">
-        <v>-0.7243976727221082</v>
+        <v>-0.7243976727221096</v>
       </c>
       <c r="G109">
-        <v>0.307659139233789</v>
+        <v>0.3076591392337882</v>
       </c>
     </row>
     <row r="110">
@@ -3322,16 +3322,16 @@
         <v>-1.548662019536432</v>
       </c>
       <c r="D110">
-        <v>-0.3410933761262996</v>
+        <v>-0.3410933761263023</v>
       </c>
       <c r="E110">
-        <v>-0.1063723969118807</v>
+        <v>-0.1063723969118783</v>
       </c>
       <c r="F110">
-        <v>1.08233431904007</v>
+        <v>1.082334319040069</v>
       </c>
       <c r="G110">
-        <v>-0.4038613754815831</v>
+        <v>-0.4038613754815842</v>
       </c>
     </row>
     <row r="111">
@@ -3349,16 +3349,16 @@
         <v>1.405739082380379</v>
       </c>
       <c r="D111">
-        <v>0.3885261428716779</v>
+        <v>0.3885261428716764</v>
       </c>
       <c r="E111">
-        <v>0.05310575588645762</v>
+        <v>0.05310575588645705</v>
       </c>
       <c r="F111">
-        <v>0.001482049488451878</v>
+        <v>0.001482049488451848</v>
       </c>
       <c r="G111">
-        <v>0.3484156847883788</v>
+        <v>0.3484156847883772</v>
       </c>
     </row>
     <row r="112">
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>-0.4880146665683487</v>
+        <v>-0.4880146665683488</v>
       </c>
       <c r="D112">
-        <v>0.7868192195070727</v>
+        <v>0.7868192195070713</v>
       </c>
       <c r="E112">
-        <v>0.3894959659501512</v>
+        <v>0.389495965950147</v>
       </c>
       <c r="F112">
-        <v>-1.289482168875674</v>
+        <v>-1.289482168875675</v>
       </c>
       <c r="G112">
-        <v>0.7408768046534612</v>
+        <v>0.7408768046534605</v>
       </c>
     </row>
     <row r="113">
@@ -3403,13 +3403,13 @@
         <v>-1.003636504906924</v>
       </c>
       <c r="D113">
-        <v>-0.1620014144397803</v>
+        <v>-0.1620014144397828</v>
       </c>
       <c r="E113">
-        <v>-0.5177479024747702</v>
+        <v>-0.5177479024747722</v>
       </c>
       <c r="F113">
-        <v>-0.7024871167986527</v>
+        <v>-0.7024871167986514</v>
       </c>
       <c r="G113">
         <v>0.3416703099748297</v>
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-1.482669153962316</v>
+        <v>-1.482669153962317</v>
       </c>
       <c r="D114">
-        <v>-1.595985863393446</v>
+        <v>-1.59598586339345</v>
       </c>
       <c r="E114">
-        <v>-1.537766989837699</v>
+        <v>-1.537766989837692</v>
       </c>
       <c r="F114">
-        <v>2.321327454323823</v>
+        <v>2.321327454323827</v>
       </c>
       <c r="G114">
-        <v>0.1470053497291559</v>
+        <v>0.1470053497291545</v>
       </c>
     </row>
     <row r="115">
@@ -3457,16 +3457,16 @@
         <v>-3.190709701370935</v>
       </c>
       <c r="D115">
-        <v>0.06663413008053203</v>
+        <v>0.06663413008052971</v>
       </c>
       <c r="E115">
-        <v>-0.4736561531244768</v>
+        <v>-0.4736561531244776</v>
       </c>
       <c r="F115">
-        <v>0.07154833539464102</v>
+        <v>0.07154833539464142</v>
       </c>
       <c r="G115">
-        <v>0.5330577141690407</v>
+        <v>0.53305771416904</v>
       </c>
     </row>
     <row r="116">
@@ -3484,16 +3484,16 @@
         <v>-1.526306834638038</v>
       </c>
       <c r="D116">
-        <v>-0.1120378252825104</v>
+        <v>-0.1120378252825124</v>
       </c>
       <c r="E116">
-        <v>0.9556781671009592</v>
+        <v>0.9556781671009565</v>
       </c>
       <c r="F116">
-        <v>-0.7484452763966565</v>
+        <v>-0.7484452763966594</v>
       </c>
       <c r="G116">
-        <v>-0.1068543262670524</v>
+        <v>-0.106854326267053</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-0.5498335179186161</v>
+        <v>-0.5498335179186162</v>
       </c>
       <c r="D117">
-        <v>0.4252881328599921</v>
+        <v>0.4252881328599889</v>
       </c>
       <c r="E117">
-        <v>-0.8440646493043285</v>
+        <v>-0.8440646493043298</v>
       </c>
       <c r="F117">
-        <v>-0.09337093572527635</v>
+        <v>-0.09337093572527494</v>
       </c>
       <c r="G117">
-        <v>-0.3436733236372376</v>
+        <v>-0.3436733236372396</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>-0.3427432526740199</v>
+        <v>-0.3427432526740202</v>
       </c>
       <c r="D118">
-        <v>0.6616535448018568</v>
+        <v>0.6616535448018555</v>
       </c>
       <c r="E118">
-        <v>0.3087850863570784</v>
+        <v>0.3087850863570802</v>
       </c>
       <c r="F118">
-        <v>1.152499573435019</v>
+        <v>1.152499573435017</v>
       </c>
       <c r="G118">
-        <v>-0.01078648607011764</v>
+        <v>-0.01078648607011958</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.610669087058248</v>
+        <v>0.6106690870582479</v>
       </c>
       <c r="D119">
-        <v>-1.385583595885103</v>
+        <v>-1.385583595885106</v>
       </c>
       <c r="E119">
-        <v>0.6189152100616523</v>
+        <v>0.6189152100616546</v>
       </c>
       <c r="F119">
-        <v>0.8384287688853965</v>
+        <v>0.8384287688853951</v>
       </c>
       <c r="G119">
-        <v>-0.3892252510278953</v>
+        <v>-0.3892252510278972</v>
       </c>
     </row>
     <row r="120">
@@ -3592,16 +3592,16 @@
         <v>1.269450518799259</v>
       </c>
       <c r="D120">
-        <v>1.663751125967077</v>
+        <v>1.663751125967075</v>
       </c>
       <c r="E120">
-        <v>-0.1380307177642</v>
+        <v>-0.1380307177642005</v>
       </c>
       <c r="F120">
         <v>0.5246169015831067</v>
       </c>
       <c r="G120">
-        <v>-0.4286967764320956</v>
+        <v>-0.4286967764320981</v>
       </c>
     </row>
     <row r="121">
@@ -3619,16 +3619,16 @@
         <v>-7.097871075087248</v>
       </c>
       <c r="D121">
-        <v>-1.843583823626117</v>
+        <v>-1.843583823626121</v>
       </c>
       <c r="E121">
-        <v>0.6468845816754779</v>
+        <v>0.6468845816754762</v>
       </c>
       <c r="F121">
-        <v>-0.5862035708518709</v>
+        <v>-0.586203570851874</v>
       </c>
       <c r="G121">
-        <v>-0.4911845922289086</v>
+        <v>-0.4911845922289083</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.1544706548251881</v>
+        <v>-0.1544706548251882</v>
       </c>
       <c r="D122">
-        <v>0.6562064101010507</v>
+        <v>0.6562064101010486</v>
       </c>
       <c r="E122">
-        <v>0.2812364003887394</v>
+        <v>0.2812364003887377</v>
       </c>
       <c r="F122">
-        <v>-0.1355535950625044</v>
+        <v>-0.1355535950625054</v>
       </c>
       <c r="G122">
-        <v>-0.3173215610580166</v>
+        <v>-0.3173215610580181</v>
       </c>
     </row>
     <row r="123">
@@ -3673,16 +3673,16 @@
         <v>1.27425629551075</v>
       </c>
       <c r="D123">
-        <v>-0.7064456093221019</v>
+        <v>-0.7064456093221032</v>
       </c>
       <c r="E123">
-        <v>0.4928111404219437</v>
+        <v>0.4928111404219451</v>
       </c>
       <c r="F123">
-        <v>0.488193772827209</v>
+        <v>0.4881937728272082</v>
       </c>
       <c r="G123">
-        <v>0.4917994917452584</v>
+        <v>0.4917994917452578</v>
       </c>
     </row>
     <row r="124">
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>-1.366952835402975</v>
+        <v>-1.366952835402974</v>
       </c>
       <c r="D124">
-        <v>1.407028535988206</v>
+        <v>1.407028535988203</v>
       </c>
       <c r="E124">
-        <v>0.07339251334613309</v>
+        <v>0.0733925133461289</v>
       </c>
       <c r="F124">
-        <v>-0.8654700989377652</v>
+        <v>-0.8654700989377662</v>
       </c>
       <c r="G124">
-        <v>-0.6771477918134685</v>
+        <v>-0.6771477918134694</v>
       </c>
     </row>
     <row r="125">
@@ -3727,16 +3727,16 @@
         <v>-1.975642105997039</v>
       </c>
       <c r="D125">
-        <v>-0.9598796149731937</v>
+        <v>-0.9598796149731963</v>
       </c>
       <c r="E125">
-        <v>-0.01459422673322573</v>
+        <v>-0.01459422673322365</v>
       </c>
       <c r="F125">
-        <v>0.8297979855695004</v>
+        <v>0.8297979855695</v>
       </c>
       <c r="G125">
-        <v>0.07940250216254091</v>
+        <v>0.07940250216254092</v>
       </c>
     </row>
     <row r="126">
@@ -3754,16 +3754,16 @@
         <v>-2.438241948161897</v>
       </c>
       <c r="D126">
-        <v>-1.014814232810781</v>
+        <v>-1.014814232810785</v>
       </c>
       <c r="E126">
-        <v>0.3865910607015278</v>
+        <v>0.3865910607015273</v>
       </c>
       <c r="F126">
-        <v>-0.03502211427480418</v>
+        <v>-0.03502211427480587</v>
       </c>
       <c r="G126">
-        <v>-0.600839592787995</v>
+        <v>-0.6008395927879966</v>
       </c>
     </row>
   </sheetData>
